--- a/dashboard/public/starter-pack/04_Bid_No_Bid_Decision_Toolkit/FLK_04_PWin_Calculator.xlsx
+++ b/dashboard/public/starter-pack/04_Bid_No_Bid_Decision_Toolkit/FLK_04_PWin_Calculator.xlsx
@@ -4,12 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Calculator" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Benchmarks" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Pipeline" state="visible" r:id="rId7"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Calculator" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Benchmarks" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Pipeline" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="PipelineStage">Lists!$A$2:$A$12</definedName>
+    <definedName name="BidDecision">Lists!$B$2:$B$6</definedName>
     <definedName name="ContractValue">Calculator!$C$8</definedName>
     <definedName name="PWin">Calculator!$C$33</definedName>
   </definedNames>
@@ -18,7 +21,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="206">
+  <si>
+    <t>Pipeline Stage</t>
+  </si>
+  <si>
+    <t>Bid Decision</t>
+  </si>
+  <si>
+    <t>Identify</t>
+  </si>
+  <si>
+    <t>BID</t>
+  </si>
+  <si>
+    <t>Qualify</t>
+  </si>
+  <si>
+    <t>No-bid</t>
+  </si>
+  <si>
+    <t>Pursue</t>
+  </si>
+  <si>
+    <t>Watch</t>
+  </si>
+  <si>
+    <t>Capture</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Pre-Sol</t>
+  </si>
+  <si>
+    <t>Subcontract</t>
+  </si>
+  <si>
+    <t>Sources Sought</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
+    <t>Won</t>
+  </si>
+  <si>
+    <t>Lost</t>
+  </si>
   <si>
     <t>PWin Calculator — How to Use This Workbook</t>
   </si>
@@ -572,12 +626,6 @@
     <t>VA-241-25-R-0012</t>
   </si>
   <si>
-    <t>Pre-Sol</t>
-  </si>
-  <si>
-    <t>BID</t>
-  </si>
-  <si>
     <t>Army Corps Levee Inspection</t>
   </si>
   <si>
@@ -585,12 +633,6 @@
   </si>
   <si>
     <t>W912EP-25-R-0007</t>
-  </si>
-  <si>
-    <t>Sources Sought</t>
-  </si>
-  <si>
-    <t>No-bid</t>
   </si>
   <si>
     <t>PIPELINE TOTALS</t>
@@ -608,12 +650,21 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -736,12 +787,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF047857"/>
+        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FF047857"/>
       </patternFill>
     </fill>
     <fill>
@@ -792,159 +843,165 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -1638,6 +1695,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF047857"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1651,162 +1800,162 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="3" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>3</v>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="72" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>3</v>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="72" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>3</v>
+      <c r="B10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>13</v>
+      <c r="B13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>3</v>
+      <c r="B14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>15</v>
+      <c r="B15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
+      <c r="B16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17" ht="90" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>17</v>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>19</v>
+      <c r="B19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>3</v>
+      <c r="B20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>21</v>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
@@ -1840,550 +1989,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="6"/>
+      <c r="B4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="6"/>
+      <c r="B5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="6"/>
+      <c r="B6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="6"/>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="6"/>
+      <c r="B8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="6"/>
+      <c r="B10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>37</v>
+      <c r="A12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="A13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+      <c r="A14" s="13">
         <v>1</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="13">
+      <c r="B14" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="15">
         <v>0.15</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15">
+      <c r="D14" s="16"/>
+      <c r="E14" s="17">
         <f>IF(D14="","",C14*D14/100)</f>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="18">
         <f>C14</f>
       </c>
-      <c r="G14" s="17"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
+      <c r="A15" s="13">
         <v>2</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="13">
+      <c r="B15" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="15">
         <v>0.1</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15">
+      <c r="D15" s="16"/>
+      <c r="E15" s="17">
         <f>IF(D15="","",C15*D15/100)</f>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="18">
         <f>C15</f>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="A16" s="13">
         <v>3</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="13">
+      <c r="B16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="15">
         <v>0.05</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="15">
+      <c r="D16" s="16"/>
+      <c r="E16" s="17">
         <f>IF(D16="","",C16*D16/100)</f>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="18">
         <f>C16</f>
       </c>
-      <c r="G16" s="17"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
+      <c r="A17" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="A18" s="13">
         <v>4</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="13">
+      <c r="B18" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="15">
         <v>0.12</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="15">
+      <c r="D18" s="16"/>
+      <c r="E18" s="17">
         <f>IF(D18="","",C18*D18/100)</f>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="18">
         <f>C18</f>
       </c>
-      <c r="G18" s="17"/>
+      <c r="G18" s="19"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
+      <c r="A19" s="13">
         <v>5</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="13">
+      <c r="B19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="15">
         <v>0.1</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15">
+      <c r="D19" s="16"/>
+      <c r="E19" s="17">
         <f>IF(D19="","",C19*D19/100)</f>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="18">
         <f>C19</f>
       </c>
-      <c r="G19" s="17"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+      <c r="A20" s="13">
         <v>6</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="13">
+      <c r="B20" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="15">
         <v>0.08</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="15">
+      <c r="D20" s="16"/>
+      <c r="E20" s="17">
         <f>IF(D20="","",C20*D20/100)</f>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="18">
         <f>C20</f>
       </c>
-      <c r="G20" s="17"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="A21" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
+      <c r="A22" s="13">
         <v>7</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="13">
+      <c r="B22" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="15">
         <v>0.08</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="15">
+      <c r="D22" s="16"/>
+      <c r="E22" s="17">
         <f>IF(D22="","",C22*D22/100)</f>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="18">
         <f>C22</f>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
+      <c r="A23" s="13">
         <v>8</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="13">
+      <c r="B23" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="15">
         <v>0.08</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="15">
+      <c r="D23" s="16"/>
+      <c r="E23" s="17">
         <f>IF(D23="","",C23*D23/100)</f>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="18">
         <f>C23</f>
       </c>
-      <c r="G23" s="17"/>
+      <c r="G23" s="19"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
+      <c r="A24" s="13">
         <v>9</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="13">
+      <c r="B24" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="15">
         <v>0.04</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15">
+      <c r="D24" s="16"/>
+      <c r="E24" s="17">
         <f>IF(D24="","",C24*D24/100)</f>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="18">
         <f>C24</f>
       </c>
-      <c r="G24" s="17"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="A25" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="A26" s="13">
         <v>10</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="13">
+      <c r="B26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="15">
         <v>0.1</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15">
+      <c r="D26" s="16"/>
+      <c r="E26" s="17">
         <f>IF(D26="","",C26*D26/100)</f>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="18">
         <f>C26</f>
       </c>
-      <c r="G26" s="17"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
+      <c r="A27" s="13">
         <v>11</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="13">
+      <c r="B27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="15">
         <v>0.05</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15">
+      <c r="D27" s="16"/>
+      <c r="E27" s="17">
         <f>IF(D27="","",C27*D27/100)</f>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="18">
         <f>C27</f>
       </c>
-      <c r="G27" s="17"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
+      <c r="A28" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
+      <c r="A29" s="13">
         <v>12</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="13">
+      <c r="B29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="15">
         <v>0.05</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="15">
+      <c r="D29" s="16"/>
+      <c r="E29" s="17">
         <f>IF(D29="","",C29*D29/100)</f>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="18">
         <f>C29</f>
       </c>
-      <c r="G29" s="17"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="19">
+      <c r="A31" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21">
         <f>SUM(C14,C15,C16,C18,C19,C20,C22,C23,C24,C26,C27,C29)</f>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="22">
         <f>IF(ABS(SUM(C14,C15,C16,C18,C19,C20,C22,C23,C24,C26,C27,C29)-1)&lt;0.001,"OK — Weights sum to 100%","Adjust column C — weights must sum to 100%")</f>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
     </row>
     <row r="33" ht="44" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="22">
+      <c r="A33" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="24">
         <f>IFERROR(SUMPRODUCT(C14:C29,D14:D29)/100,0)</f>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="23">
+      <c r="D33" s="24"/>
+      <c r="E33" s="25">
         <f>IF(C33&gt;=0.7,"STRONG — Commit full capture resources",IF(C33&gt;=0.5,"MODERATE — Go if no better alternative",IF(C33&gt;=0.3,"MARGINAL — Requires gap closure plan","LOW — Reconsider or pass")))</f>
       </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="24">
+      <c r="A34" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="26">
         <f>IFERROR(ContractValue*PWin,0)</f>
       </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
+      <c r="A36" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
     </row>
     <row r="37" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="28"/>
+      <c r="B37" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="30"/>
     </row>
     <row r="38" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="29">
+      <c r="B38" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="31">
         <f>IFERROR(C37/ContractValue,0)</f>
       </c>
-      <c r="D38" s="29"/>
+      <c r="D38" s="31"/>
     </row>
     <row r="39" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="29">
+      <c r="B39" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="31">
         <f>IFERROR(C37/C34,0)</f>
       </c>
-      <c r="D39" s="29"/>
+      <c r="D39" s="31"/>
     </row>
     <row r="40" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="30">
+      <c r="B40" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="32">
         <f>IF(C34&gt;C37,"OK — Expected value exceeds B&amp;P spend","Risk — B&amp;P spend exceeds expected value")</f>
       </c>
-      <c r="D40" s="30"/>
+      <c r="D40" s="32"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
+      <c r="A43" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -2624,7 +2773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0F172A"/>
@@ -2641,500 +2790,500 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="A2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="A4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>77</v>
+      <c r="A5" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>81</v>
+      <c r="A6" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>85</v>
+      <c r="A7" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>89</v>
+      <c r="A8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>93</v>
+      <c r="A9" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>37</v>
+      <c r="A12" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>101</v>
+      <c r="A13" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>105</v>
+      <c r="A14" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>109</v>
+      <c r="A15" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>113</v>
+      <c r="A16" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>117</v>
+      <c r="A17" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>121</v>
+      <c r="A18" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
+      <c r="A20" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>37</v>
+      <c r="A21" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>129</v>
+      <c r="A22" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>133</v>
+      <c r="A23" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>137</v>
+      <c r="A24" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>140</v>
+      <c r="A25" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" s="33" t="s">
-        <v>144</v>
+      <c r="A26" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="A28" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>149</v>
+      <c r="A29" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>153</v>
+      <c r="A30" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="D31" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>157</v>
+      <c r="A31" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>161</v>
+      <c r="A32" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="34" t="s">
-        <v>164</v>
+      <c r="A33" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>167</v>
+      <c r="A34" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" s="34" t="s">
+      <c r="A35" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="D36" s="35" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" s="33" t="s">
-        <v>172</v>
+      <c r="E36" s="35" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3155,7 +3304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
@@ -3176,424 +3325,424 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>180</v>
+      <c r="A2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" s="38">
+      <c r="A3" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="40">
         <v>2400000</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>0.51</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="41">
         <f>IFERROR(D3*E3,0)</f>
       </c>
-      <c r="G3" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="H3" s="40">
+      <c r="G3" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="42">
         <v>46280.25</v>
       </c>
-      <c r="I3" s="37" t="s">
-        <v>185</v>
+      <c r="I3" s="39" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="44">
+      <c r="A4" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="46">
         <v>850000</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="47">
         <v>0.32</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="48">
         <f>IFERROR(D4*E4,0)</f>
       </c>
-      <c r="G4" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="47">
+      <c r="G4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="49">
         <v>46325.25</v>
       </c>
-      <c r="I4" s="43" t="s">
-        <v>190</v>
+      <c r="I4" s="45" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="39">
+      <c r="A5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="41">
         <f>IFERROR(D5*E5,0)</f>
       </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="37"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="46">
+      <c r="A6" s="43"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="48">
         <f>IFERROR(D6*E6,0)</f>
       </c>
-      <c r="G6" s="43"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="43"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="45"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="39">
+      <c r="A7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="41">
         <f>IFERROR(D7*E7,0)</f>
       </c>
-      <c r="G7" s="37"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="37"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="39"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="46">
+      <c r="A8" s="43"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="48">
         <f>IFERROR(D8*E8,0)</f>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="43"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="45"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="39">
+      <c r="A9" s="37"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="41">
         <f>IFERROR(D9*E9,0)</f>
       </c>
-      <c r="G9" s="37"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="37"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="46">
+      <c r="A10" s="43"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="48">
         <f>IFERROR(D10*E10,0)</f>
       </c>
-      <c r="G10" s="43"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="43"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="45"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="39">
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="41">
         <f>IFERROR(D11*E11,0)</f>
       </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="37"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="41"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="46">
+      <c r="A12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48">
         <f>IFERROR(D12*E12,0)</f>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="43"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="45"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="39">
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="41">
         <f>IFERROR(D13*E13,0)</f>
       </c>
-      <c r="G13" s="37"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="37"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="39"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="41"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="46">
+      <c r="A14" s="43"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48">
         <f>IFERROR(D14*E14,0)</f>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="43"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="45"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="39">
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="41">
         <f>IFERROR(D15*E15,0)</f>
       </c>
-      <c r="G15" s="37"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="37"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="39"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="41"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="46">
+      <c r="A16" s="43"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48">
         <f>IFERROR(D16*E16,0)</f>
       </c>
-      <c r="G16" s="43"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="43"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="45"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="39">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="41">
         <f>IFERROR(D17*E17,0)</f>
       </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="37"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="39"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="41"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="46">
+      <c r="A18" s="43"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="48">
         <f>IFERROR(D18*E18,0)</f>
       </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="43"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="45"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="39">
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="41">
         <f>IFERROR(D19*E19,0)</f>
       </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="37"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="41"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="46">
+      <c r="A20" s="43"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48">
         <f>IFERROR(D20*E20,0)</f>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="43"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="45"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="39">
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="41">
         <f>IFERROR(D21*E21,0)</f>
       </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="37"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="39"/>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="41"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="46">
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48">
         <f>IFERROR(D22*E22,0)</f>
       </c>
-      <c r="G22" s="43"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="43"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="45"/>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="39">
+      <c r="A23" s="37"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="41">
         <f>IFERROR(D23*E23,0)</f>
       </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="37"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="39"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="41"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="46">
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48">
         <f>IFERROR(D24*E24,0)</f>
       </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="43"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="45"/>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="39">
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="41">
         <f>IFERROR(D25*E25,0)</f>
       </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="37"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="39"/>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="46">
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48">
         <f>IFERROR(D26*E26,0)</f>
       </c>
-      <c r="G26" s="43"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="43"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="45"/>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="39">
+      <c r="A27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="41">
         <f>IFERROR(D27*E27,0)</f>
       </c>
-      <c r="G27" s="37"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="37"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="39"/>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="48" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="49">
+      <c r="A28" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51">
         <f>SUM(D3:D27)</f>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IFERROR(SUMPRODUCT(D3:D27,E3:E27)/SUM(D3:D27),0)</f>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="51">
         <f>SUM(F3:F27)</f>
       </c>
-      <c r="G28" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
+      <c r="G28" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3623,16 +3772,16 @@
       <formula2>1</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid stage" error="Pick from the dropdown." sqref="G10:G27">
-      <formula1>"Identify,Qualify,Pursue,Capture,Pre-Sol,Sources Sought,Proposal,Submitted,Won,Lost,No-bid"</formula1>
+      <formula1>PipelineStage</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid stage" error="Pick from the dropdown." sqref="G3:G27">
-      <formula1>"Identify,Qualify,Pursue,Capture,Pre-Sol,Sources Sought,Proposal,Submitted,Won,Lost,No-bid"</formula1>
+      <formula1>PipelineStage</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid decision" error="Pick from the dropdown." sqref="I10:I27">
-      <formula1>"BID,No-bid,Watch,Team,Subcontract"</formula1>
+      <formula1>BidDecision</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid decision" error="Pick from the dropdown." sqref="I3:I27">
-      <formula1>"BID,No-bid,Watch,Team,Subcontract"</formula1>
+      <formula1>BidDecision</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
